--- a/output/pdf_financials_xlsx/SILV.xlsx
+++ b/output/pdf_financials_xlsx/SILV.xlsx
@@ -5711,52 +5711,52 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>9.581219000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>9.716970999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>11.059726</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>11.364024</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>11.510998</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>7.307904</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>7.417539</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>7.90315</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>8.198924999999999</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>8.205700999999999</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>8.205700999999999</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>8.582890000000001</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>8.839935000000001</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>9.063596</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>9.126753000000001</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>9.127821000000001</v>
       </c>
     </row>
     <row r="93">
@@ -7186,13 +7186,13 @@
         </is>
       </c>
       <c r="C118" s="3" t="n">
-        <v>9.612246000000001</v>
+        <v>7.208611</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>2.597917</v>
+        <v>-0.590992</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.000394</v>
+        <v>-0.129155</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -7201,34 +7201,34 @@
         <v>0.678771</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0</v>
+        <v>-0.028283</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.294212</v>
+        <v>-0.76762</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.42</v>
+        <v>0.08146100000000001</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0</v>
+        <v>-0.125475</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.002599</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.082743</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.075726</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-0.709432</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.539978</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.511328</v>
       </c>
     </row>
     <row r="119">
@@ -9662,7 +9662,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11330,7 +11334,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -13408,7 +13416,11 @@
           <t>Reserves (Note 7)</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14248,7 +14260,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>9.581219000000001</v>
       </c>
@@ -17862,7 +17878,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -19228,7 +19248,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr"/>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -21622,7 +21646,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -23166,7 +23194,11 @@
           <t>Non-cash exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -26140,7 +26172,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SILV.xlsx
+++ b/output/pdf_financials_xlsx/SILV.xlsx
@@ -1020,10 +1020,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.241839</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.296247</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1953,10 +1953,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>15.084428</v>
+        <v>14.842589</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-13.851745</v>
+        <v>-14.147992</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-7.151682</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>15.084428</v>
+        <v>14.842589</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-13.851745</v>
+        <v>-14.147992</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-7.151682</v>
@@ -2357,22 +2357,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.151133</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.057517</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.176895</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.01227</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.161589</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.030492</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.898134</v>
@@ -2381,10 +2381,10 @@
         <v>0.278946</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.473267</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.060141</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0.063791</v>
@@ -2467,22 +2467,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.151133</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.057517</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.176895</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.01227</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.161589</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.030492</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.898134</v>
@@ -2491,10 +2491,10 @@
         <v>0.278946</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.473267</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.060141</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0.063791</v>
@@ -3127,22 +3127,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>9.152602</v>
+        <v>9.001469</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>12.507878</v>
+        <v>12.450361</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>7.330972</v>
+        <v>7.154077</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.244953</v>
+        <v>1.232683</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.60784</v>
+        <v>1.446251</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.165671</v>
+        <v>1.135179</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.003452</v>
@@ -3151,10 +3151,10 @@
         <v>0.010329</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.479995</v>
+        <v>0.006728</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.091683</v>
+        <v>0.031542</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0</v>
@@ -11904,7 +11904,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E40" s="5" t="n">
@@ -44334,7 +44334,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">

--- a/output/pdf_financials_xlsx/SILV.xlsx
+++ b/output/pdf_financials_xlsx/SILV.xlsx
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-3.599426</v>
+        <v>1.410567</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>3.13695</v>
+        <v>-0.438859</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>0.322014</v>
+        <v>-0.104691</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.327017</v>
+        <v>-0.867017</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -2211,16 +2211,16 @@
         </is>
       </c>
       <c r="C31" s="3" t="n">
-        <v>23.861866025016</v>
+        <v>9.351146758763408</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-22.64660517501585</v>
+        <v>-3.168257862096075</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-4.502633086873829</v>
+        <v>-1.463865423546517</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>-13.67007341743684</v>
+        <v>-36.24333305047088</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>-0</v>
@@ -6805,22 +6805,22 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.01432</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005469</v>
       </c>
       <c r="K111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.000874</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N111" s="3" t="n">
-        <v>0</v>
+        <v>-0.003209</v>
       </c>
       <c r="O111" s="3" t="n">
         <v>0</v>
@@ -8166,22 +8166,22 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.01432</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005469</v>
       </c>
       <c r="K134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.000874</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="N134" s="3" t="n">
-        <v>0</v>
+        <v>-0.003209</v>
       </c>
       <c r="O134" s="3" t="n">
         <v>0</v>
@@ -8223,22 +8223,22 @@
         <v>-0.198627</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.350021</v>
+        <v>-0.364341</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-0.87025</v>
+        <v>-0.875719</v>
       </c>
       <c r="K135" s="3" t="n">
         <v>-0.347651</v>
       </c>
       <c r="L135" s="3" t="n">
-        <v>-0.430877</v>
+        <v>-0.431751</v>
       </c>
       <c r="M135" s="3" t="n">
         <v>-0.403808</v>
       </c>
       <c r="N135" s="3" t="n">
-        <v>-0.247878</v>
+        <v>-0.251087</v>
       </c>
       <c r="O135" s="3" t="n">
         <v>-0.328264</v>
@@ -19926,7 +19926,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
           <t>-</t>
@@ -20394,7 +20398,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr"/>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E131" t="inlineStr">
         <is>
           <t>-</t>
@@ -21744,7 +21752,11 @@
           <t>Purchases of equipment</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E145" t="inlineStr">
         <is>
           <t>-</t>
@@ -24732,7 +24744,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr"/>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E176" t="inlineStr">
         <is>
           <t>-</t>
@@ -27132,7 +27148,11 @@
           <t>Acquisition of shares of Coro Mining Corp. in private placement</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -27684,7 +27704,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -29586,7 +29610,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -40624,7 +40652,11 @@
           <t>Current income tax recovery</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -41942,7 +41974,11 @@
           <t>Current income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D359" t="inlineStr"/>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E359" t="inlineStr">
         <is>
           <t>-</t>
@@ -42036,7 +42072,11 @@
           <t>Deferred income tax recovery (note 10)</t>
         </is>
       </c>
-      <c r="D360" t="inlineStr"/>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E360" t="inlineStr">
         <is>
           <t>-</t>
@@ -43470,7 +43510,11 @@
           <t>Current income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -43564,7 +43608,11 @@
           <t>Deferred income tax recovery (note 12)</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr"/>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E376" t="inlineStr">
         <is>
           <t>-</t>
@@ -45102,7 +45150,11 @@
           <t>Current income tax recovery (expense) (note 12(a))</t>
         </is>
       </c>
-      <c r="D392" t="inlineStr"/>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E392" t="inlineStr">
         <is>
           <t>-</t>
@@ -45196,7 +45248,11 @@
           <t>Deferred income tax recovery (expense) (note 12(a))</t>
         </is>
       </c>
-      <c r="D393" t="inlineStr"/>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E393" t="inlineStr">
         <is>
           <t>-</t>
